--- a/extenbooks/S1508_extenbook.xlsx
+++ b/extenbooks/S1508_extenbook.xlsx
@@ -2099,7 +2099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -2951,11 +2951,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2978,64 +2978,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1508</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1508_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1508_DPR.md", "epr": "Technical/docs/series/S1508_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1508_load.py", "processor": "Technical/code/P02_processors/P02_S1508_construct.py", "validator": "Technical/code/V03_validators/V03_S1508_validate.py", "processed": "Technical/data/processed/S1508.parquet", "chopped_csv": "Technical/chopped/S1508.csv", "extenbook_xlsx": "Technical/extenbooks/S1508_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1508_extenbook.xlsx
+++ b/extenbooks/S1508_extenbook.xlsx
@@ -2046,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A107"/>
+  <dimension ref="A1:A109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2085,7 +2085,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>**Phase 4 corrections**: Figure caption says "table 12.1"; correct is **table 12.11** (per narrative + Appendix 15.1 p.897).</t>
+          <t>**Data-adequacy review corrections**: Figure caption says "table 12.1"; correct is **table 12.11** (per narrative + Appendix 15.1 p.897).</t>
         </is>
       </c>
     </row>
@@ -2224,38 +2224,38 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units |</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1508-A, S1508-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>| **S1508-lambda** | 29 country-periods within 1970-1988 | Harberger (1988) table 12.11, reproduced in `Appendix15_WorldInflationDataLambda.xlsx` sheet `HarbergerTable12` col 0 | Rate (percent) |</t>
+          <t>| Subseries | Coverage | Source | Native units |</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| **S1508-pi** | 29 country-periods | Harberger (1988) table 12.11, same xlsx col 1 | Rate (percent) |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>| **S1508-lambda** | 29 country-periods within 1970-1988 | Harberger (1988) table 12.11, reproduced in `Appendix15_WorldInflationDataLambda.xlsx` sheet `HarbergerTable12` col 0 | Rate (percent) |</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Underlying data source: IMF IFS legacy line 32 (Total Domestic Claims). Modern IMF SDMX 3.0 equivalent: `DCORP_N_DC` in dataflow `MFS_DC`. See `_imf_ifs_resolver.py` for the documented mapping. Re-fetch is feasible for cross-validation but the published Harberger values are the canonical replication target.</t>
+          <t>| **S1508-pi** | 29 country-periods | Harberger (1988) table 12.11, same xlsx col 1 | Rate (percent) |</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>Underlying data source: IMF IFS legacy line 32 (Total Domestic Claims). Modern IMF SDMX (Statistical Data and Metadata eXchange) 3.0 equivalent: `DCORP_N_DC` in dataflow `MFS_DC`. See `_imf_ifs_resolver.py` for the documented mapping. Re-fetch is feasible for cross-validation but the published Harberger values are the canonical replication target.</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>`direct` (cross_sectional): the loader reads the 29 (lambda, pi) pairs verbatim from the chopped table. No formula applied.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>`direct` (cross_sectional): the loader reads the 29 (lambda, pi) pairs verbatim from the chopped table. No formula applied.</t>
         </is>
       </c>
     </row>
@@ -2295,24 +2295,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>- **Book**: 1970-1988 (29 country-period averages, not annual)</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>- **Extension**: **not_applicable_cross_sectional** — Harberger's panel is a published historical snapshot. A modern re-pull (29 countries 1970-1988) via the IMF resolver is feasible as Phase 6+ enrichment, not as primary extension.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Extension**: **not_applicable_cross_sectional** — Harberger's panel is a published historical snapshot. A modern re-pull (29 countries 1970-1988) via the IMF resolver is feasible as a later enrichment pass, not as primary extension.</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Rate (percent). Note: distinct from US-side decimal-rate convention.</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>Rate (percent). Note: distinct from US-side decimal-rate convention.</t>
         </is>
       </c>
     </row>
@@ -2342,31 +2342,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1. **Cross_sectional**: no time series; no per-year extension.</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2. **IMF IFS code remap** documented in `_imf_ifs_resolver.LINE_TO_MODERN[32]` for any future modern re-pull. Code remap, not concept proxy.</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3. **Country labels not in chopped file**: the `Appendix15_WorldInflationDataLambda.xlsx` Harberger table is 2-column (lambda, pi) without country names. The country roster lives in the book's Appendix 15.1 p.897 and is replicated in the registry's `S1508` subseries metadata.</t>
+          <t>1. **Cross_sectional**: no time series; no per-year extension.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2. **IMF IFS code remap** documented in `_imf_ifs_resolver.LINE_TO_MODERN[32]` for any future modern re-pull. Code remap, not concept proxy.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>3. **Country labels not in chopped file**: the `Appendix15_WorldInflationDataLambda.xlsx` Harberger table is 2-column (lambda, pi) without country names. The country roster lives in the book's Appendix 15.1 p.897 and is replicated in the registry's `S1508` subseries metadata.</t>
         </is>
       </c>
     </row>
@@ -2376,24 +2376,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S080`</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figure 15.12 (caption typo "table 12.1" -&gt; "table 12.11"); Appendix 15.1 p. 897</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>- **Predecessor-build ID**: `S080`</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figure 15.12 (caption typo "table 12.1" -&gt; "table 12.11"); Appendix 15.1 p. 897</t>
         </is>
       </c>
     </row>
@@ -2403,82 +2403,82 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>- **Tolerance**: +/- 0.5% per cell (29 lambda + 29 pi = 58 cells) against the chopped table.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>- **Expected MAE**: zero (we read the same column).</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>- **Expected mean absolute error (MAE)**: zero (we read the same column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4">
         <f>== EPR: S1508_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t># S1508 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>**Series**: S1508 — Harberger 29-country cross-section, 1970-1988</t>
+          <t># S1508 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>**Construction classification**: `direct` (`cross_sectional` content type)</t>
+          <t>**Series**: S1508 — Harberger 29-country cross-section, 1970-1988</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>**Extension method**: **not_applicable_cross_sectional**</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Construction classification**: `direct` (`cross_sectional` content type)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Extension method**: **not_applicable_cross_sectional**</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>## 1. Why no time-series extension</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S1508 is `cross_sectional`. It is a 29-country snapshot of period averages within 1970-1988. There is no concept of "extending it to 2025"; the snapshot is the data.</t>
+          <t>## 1. Why no time-series extension</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>## 2. Optional modern re-pull (Phase 6+ enrichment, not extension)</t>
+          <t>S1508 is `cross_sectional`. It is a 29-country snapshot of period averages within 1970-1988. There is no concept of "extending it to 2025"; the snapshot is the data.</t>
         </is>
       </c>
     </row>
@@ -2518,83 +2518,83 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>If one wanted to re-construct Harberger's panel from modern IFS data, the recipe is:</t>
+          <t>## 2. Optional modern re-pull (later enrichment pass, not extension)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>- For each of the 29 countries, fetch IMF MFS_DC `DCORP_N_DC` and CPI `PCPI_IX` for the country-specific period</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>- Compute period-average growth rates and inflation</t>
+          <t>If one wanted to re-construct Harberger's panel from modern IFS data, the recipe is:</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>- Compare against Harberger's published values</t>
+          <t>- For each of the 29 countries, fetch IMF MFS_DC `DCORP_N_DC` and CPI `PCPI_IX` for the country-specific period</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>- Compute period-average growth rates and inflation</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>This uses `_imf_ifs_resolver`:</t>
+          <t>- Compare against Harberger's published values</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>```python</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>from loaders._imf_ifs_resolver import resolve_ifs_line, fetch_ifs_series</t>
+          <t>This uses `_imf_ifs_resolver`:</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>modern_credit = resolve_ifs_line(32)   # -&gt; "DCORP_N_DC"</t>
+          <t>```python</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>modern_cpi    = resolve_ifs_line(64)   # -&gt; "PCPI_IX"</t>
+          <t>from loaders._imf_ifs_resolver import resolve_ifs_line, fetch_ifs_series</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>modern_credit = resolve_ifs_line(32)   # -&gt; "DCORP_N_DC"</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>modern_cpi    = resolve_ifs_line(64)   # -&gt; "PCPI_IX"</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>This is **not** executed in the standard pipeline (cross_sectional series have no extension), but the resolver integration is documented here.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>## 3. No proxy</t>
+          <t>This is **not** executed in the standard pipeline (cross_sectional series have no extension), but the resolver integration is documented here.</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>The Harberger table reproduces IMF IFS line 32 values for 29 countries — Shaikh's exact source.</t>
+          <t>## 3. No proxy</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>## 4. No synthetic data</t>
+          <t>The Harberger table reproduces IMF IFS line 32 values for 29 countries — Shaikh's exact source.</t>
         </is>
       </c>
     </row>
@@ -2633,6 +2633,16 @@
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
+        <is>
+          <t>## 4. No synthetic data</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Verbatim load. No interpolation. No country imputation.</t>
         </is>
@@ -2807,11 +2817,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2853,7 +2863,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2931,12 +2941,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>independent_anchors</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"status": "GREEN", "any_red": false, "anchors": {"status": "GREEN", "sid": "S1508", "n_anchors": 6, "n_red": 0, "n_green": 6, "n_na": 0, "anchors": [{"anchor_id": "S1508_H01_lambda", "anchor_type": "point", "subseries_id": "S1508-lambda", "source_description": "Harberger (1988) growth-of-Domestic-Claims (lambda=gDC), country H01. Transcribed in S1508 MHR SS5 + CH15_review hand_checks[4] (independent of loader path).", "status": "GREEN", "expected": 3.123, "actual": 3.123, "detail": "country_key=H01", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S1508_H02_lambda", "anchor_type": "point", "subseries_id": "S1508-lambda", "source_description": "Harberger (1988) lambda=gDC, country H02 (MHR SS5 + CH15_review hand_checks[4]).", "status": "GREEN", "expected": 3.432, "actual": 3.432, "detail": "country_key=H02", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S1508_H03_lambda", "anchor_type": "point", "subseries_id": "S1508-lambda", "source_description": "Harberger (1988) lambda=gDC, country H03 (MHR SS5 + CH15_review hand_checks[4]).", "status": "GREEN", "expected": 1.421, "actual": 1.421, "detail": "country_key=H03", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S1508_H01_pi", "anchor_type": "point", "subseries_id": "S1508-pi", "source_description": "Harberger (1988) inflation (pi), country H01 (MHR SS5 + CH15_review hand_checks[4]).", "status": "GREEN", "expected": 2.546, "actual": 2.546, "detail": "country_key=H01", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S1508_H02_pi", "anchor_type": "point", "subseries_id": "S1508-pi", "source_description": "Harberger (1988) inflation (pi), country H02 (MHR SS5 + CH15_review hand_checks[4]).", "status": "GREEN", "expected": 2.69, "actual": 2.69, "detail": "country_key=H02", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}, {"anchor_id": "S1508_H03_pi", "anchor_type": "point", "subseries_id": "S1508-pi", "source_description": "Harberger (1988) inflation (pi), country H03 (MHR SS5 + CH15_review hand_checks[4]).", "status": "GREEN", "expected": 1.23, "actual": 1.23, "detail": "country_key=H03", "abs_pct_diff": 0.0, "tolerance_pct": 1.0}]}, "splice": {"status": "NA", "sid": "S1508", "detail": "no extension / no book+extension ranges"}, "plausibility": {"status": "NA", "sid": "S1508", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>validated_at</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:14:08.314218+00:00</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-02T06:19:53.561844+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1508_extenbook.xlsx
+++ b/extenbooks/S1508_extenbook.xlsx
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02T06:19:53.561844+00:00</t>
+          <t>2026-07-11T03:44:23.488558+00:00</t>
         </is>
       </c>
     </row>
@@ -2973,11 +2973,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3000,6 +3000,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HARBERGER_1988_TABLE_12_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful direct replication of book figure 15.12 - Harberger's 29-country cross-section of inflation versus domestic-credit growth. Cross-sectional (country panel), so the single year label (1988, the period end) is correct and the COVERAGE_START prescreen flag is an index-axis false positive (these are not a time series). Anchor verified: country H01 = Argentina, pi 2.546 / lambda 3.123, matching the book's '255% inflation, 312% credit growth' for Argentina 1982-1984.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1508_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1508_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cross_sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
